--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6469-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6469-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{510F090F-1F5F-4D5E-AC08-41B75F104389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92A8A26F-4183-454B-A7FD-37DB31DDA9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{6608FE0B-8D66-41EA-9BD5-4EDE9DEAF12E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{7064AC51-EFAA-4A0C-8AC9-FF7F6181A31D}"/>
   </bookViews>
   <sheets>
     <sheet name="6469-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1538,29 +1538,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F732234F-016E-4098-9344-0BFC0C2B43C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA91713-EFD2-4E46-8D0C-1D94FBC82C63}">
   <dimension ref="A1:X26"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.75" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1594,7 +1593,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1630,7 +1629,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1682,7 +1681,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1750,7 +1749,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1822,7 +1821,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="13" t="s">
@@ -1850,7 +1849,7 @@
       <c r="W6" s="46"/>
       <c r="X6" s="42"/>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>2023</v>
       </c>
@@ -1922,7 +1921,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="49"/>
       <c r="B8" s="50"/>
       <c r="C8" s="16" t="s">
@@ -1950,7 +1949,7 @@
       <c r="W8" s="56"/>
       <c r="X8" s="52"/>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2022</v>
       </c>
@@ -2022,7 +2021,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39"/>
       <c r="B10" s="40"/>
       <c r="C10" s="13" t="s">
@@ -2050,7 +2049,7 @@
       <c r="W10" s="46"/>
       <c r="X10" s="42"/>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>2021</v>
       </c>
@@ -2122,7 +2121,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="49"/>
       <c r="B12" s="50"/>
       <c r="C12" s="16" t="s">
@@ -2150,7 +2149,7 @@
       <c r="W12" s="56"/>
       <c r="X12" s="52"/>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2020</v>
       </c>
@@ -2222,7 +2221,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39"/>
       <c r="B14" s="40"/>
       <c r="C14" s="13" t="s">
@@ -2250,7 +2249,7 @@
       <c r="W14" s="46"/>
       <c r="X14" s="42"/>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="47">
         <v>2019</v>
       </c>
@@ -2322,7 +2321,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="16" t="s">
@@ -2350,7 +2349,7 @@
       <c r="W16" s="56"/>
       <c r="X16" s="52"/>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2018</v>
       </c>
@@ -2422,7 +2421,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39"/>
       <c r="B18" s="40"/>
       <c r="C18" s="13" t="s">
@@ -2450,7 +2449,7 @@
       <c r="W18" s="46"/>
       <c r="X18" s="42"/>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="57">
         <v>2017</v>
       </c>
@@ -2522,7 +2521,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="59">
         <v>2016</v>
       </c>
@@ -2594,7 +2593,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="47">
         <v>2015</v>
       </c>
@@ -2666,7 +2665,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="49"/>
       <c r="B22" s="50"/>
       <c r="C22" s="16" t="s">
@@ -2694,7 +2693,7 @@
       <c r="W22" s="56"/>
       <c r="X22" s="52"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2014</v>
       </c>
@@ -2766,7 +2765,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39"/>
       <c r="B24" s="40"/>
       <c r="C24" s="13" t="s">
@@ -2794,7 +2793,7 @@
       <c r="W24" s="46"/>
       <c r="X24" s="42"/>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="57">
         <v>2013</v>
       </c>
@@ -2866,7 +2865,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="59" t="s">
         <v>48</v>
       </c>
